--- a/overview.xlsx
+++ b/overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>ASR: 0.8197 | V1: 61</t>
-  </si>
-  <si>
-    <t>ASR: 0.4359 | V1: 39</t>
   </si>
   <si>
     <t>ASR: 0.4812 | V1: 133</t>
@@ -492,10 +489,10 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,13 +506,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -525,20 +522,17 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -46,49 +46,43 @@
     <t>Llama-3.3-70B-Instruct</t>
   </si>
   <si>
+    <t>ASR: 0.2308 | V1: 52</t>
+  </si>
+  <si>
     <t>ASR: 0.2016 | V1: 129</t>
   </si>
   <si>
+    <t>ASR: 0.6098 | V1: 41</t>
+  </si>
+  <si>
     <t>ASR: 0.8148 | V1: 81</t>
   </si>
   <si>
-    <t>ASR: 0.8500 | V1: 40</t>
-  </si>
-  <si>
-    <t>ASR: 0.6098 | V1: 41</t>
-  </si>
-  <si>
     <t>ASR: 0.4130 | V1: 92</t>
   </si>
   <si>
     <t>ASR: 0.8197 | V1: 61</t>
   </si>
   <si>
+    <t>ASR: 0.2889 | V1: 90</t>
+  </si>
+  <si>
     <t>ASR: 0.4812 | V1: 133</t>
   </si>
   <si>
-    <t>ASR: 0.2889 | V1: 90</t>
-  </si>
-  <si>
     <t>ASR: 0.6176 | V1: 34</t>
   </si>
   <si>
-    <t>ASR: 0.7797 | V1: 118</t>
+    <t>ASR: 0.6724 | V1: 58</t>
   </si>
   <si>
     <t>ASR: 0.7091 | V1: 110</t>
   </si>
   <si>
-    <t>ASR: 0.6724 | V1: 58</t>
+    <t>ASR: 0.7500 | V1: 36</t>
   </si>
   <si>
     <t>ASR: 0.9483 | V1: 58</t>
-  </si>
-  <si>
-    <t>ASR: 0.9828 | V1: 58</t>
-  </si>
-  <si>
-    <t>ASR: 0.7500 | V1: 36</t>
   </si>
 </sst>
 </file>
@@ -477,62 +471,56 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
       <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>ASR: 0.9483 | V1: 58</t>
+  </si>
+  <si>
+    <t>ASR: 0.9828 | V1: 58</t>
   </si>
 </sst>
 </file>
@@ -522,6 +525,9 @@
       <c r="G4" t="s">
         <v>20</v>
       </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="ASR Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="ASR-Overview" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -40,52 +40,89 @@
     <t>Judge Model</t>
   </si>
   <si>
+    <t>Llama-3.3-70B-Instruct</t>
+  </si>
+  <si>
     <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
-    <t>Llama-3.3-70B-Instruct</t>
-  </si>
-  <si>
-    <t>ASR: 0.2308 | V1: 52</t>
-  </si>
-  <si>
-    <t>ASR: 0.2016 | V1: 129</t>
-  </si>
-  <si>
-    <t>ASR: 0.6098 | V1: 41</t>
-  </si>
-  <si>
-    <t>ASR: 0.8148 | V1: 81</t>
-  </si>
-  <si>
-    <t>ASR: 0.4130 | V1: 92</t>
-  </si>
-  <si>
-    <t>ASR: 0.8197 | V1: 61</t>
-  </si>
-  <si>
-    <t>ASR: 0.2889 | V1: 90</t>
-  </si>
-  <si>
-    <t>ASR: 0.4812 | V1: 133</t>
-  </si>
-  <si>
-    <t>ASR: 0.6176 | V1: 34</t>
-  </si>
-  <si>
-    <t>ASR: 0.6724 | V1: 58</t>
-  </si>
-  <si>
-    <t>ASR: 0.7091 | V1: 110</t>
-  </si>
-  <si>
-    <t>ASR: 0.7500 | V1: 36</t>
-  </si>
-  <si>
-    <t>ASR: 0.9483 | V1: 58</t>
-  </si>
-  <si>
-    <t>ASR: 0.9828 | V1: 58</t>
+    <t>phi-4</t>
+  </si>
+  <si>
+    <t>ASR: 0.20
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>ASR: 0.57
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR: 0.23
+V1: 52 V2: 10 Vties: 76</t>
+  </si>
+  <si>
+    <t>ASR: 0.81
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
+    <t>ASR: 0.78
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR: 0.61
+V1: 41 V2: 10 Vties: 89</t>
+  </si>
+  <si>
+    <t>ASR: 0.82
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
+    <t>ASR: 0.77
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.48
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR: 0.22
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>ASR: 0.29
+V1: 90 V2: 1 Vties: 50</t>
+  </si>
+  <si>
+    <t>ASR: 0.82
+V1: 49 V2: 53 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR: 0.62
+V1: 34 V2: 15 Vties: 92</t>
+  </si>
+  <si>
+    <t>ASR: 0.71
+V1: 110 V2: 12 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR: 0.67
+V1: 58 V2: 11 Vties: 72</t>
+  </si>
+  <si>
+    <t>ASR: 0.98
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>ASR: 0.95
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>ASR: 0.75
+V1: 36 V2: 7 Vties: 99</t>
   </si>
 </sst>
 </file>
@@ -144,8 +181,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -443,90 +483,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="ASR-Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="AASR-Overview" sheetId="2" r:id="rId2"/>
+    <sheet name="FR-Overview" sheetId="3" r:id="rId3"/>
+    <sheet name="CR-Overview" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="95">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -109,6 +112,10 @@
 V1: 110 V2: 12 Vties: 20</t>
   </si>
   <si>
+    <t>ASR: 0.69
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
     <t>ASR: 0.67
 V1: 58 V2: 11 Vties: 72</t>
   </si>
@@ -121,7 +128,263 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
+    <t>ASR: 0.98
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
     <t>ASR: 0.75
+V1: 36 V2: 7 Vties: 99</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 52 V2: 10 Vties: 76</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 41 V2: 10 Vties: 89</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 90 V2: 1 Vties: 50</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 49 V2: 53 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 34 V2: 15 Vties: 92</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 110 V2: 12 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 58 V2: 11 Vties: 72</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 36 V2: 7 Vties: 99</t>
+  </si>
+  <si>
+    <t>FR: 0.26
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>FR: 0.56
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>FR: 0.64
+V1: 52 V2: 10 Vties: 76</t>
+  </si>
+  <si>
+    <t>FR: 0.76
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
+    <t>FR: 0.62
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
+    <t>FR: 0.81
+V1: 41 V2: 10 Vties: 89</t>
+  </si>
+  <si>
+    <t>FR: 0.68
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
+    <t>FR: 0.51
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
+    <t>FR: 0.67
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.49
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>FR: 0.25
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>FR: 0.54
+V1: 90 V2: 1 Vties: 50</t>
+  </si>
+  <si>
+    <t>FR: 0.47
+V1: 49 V2: 53 Vties: 16</t>
+  </si>
+  <si>
+    <t>FR: 0.80
+V1: 34 V2: 15 Vties: 92</t>
+  </si>
+  <si>
+    <t>FR: 0.69
+V1: 110 V2: 12 Vties: 20</t>
+  </si>
+  <si>
+    <t>FR: 0.66
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
+    <t>FR: 0.79
+V1: 58 V2: 11 Vties: 72</t>
+  </si>
+  <si>
+    <t>FR: 0.79
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>FR: 0.89
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>FR: 0.78
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>FR: 0.89
+V1: 36 V2: 7 Vties: 99</t>
+  </si>
+  <si>
+    <t>CR: 0.80
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>CR: 0.45
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 52 V2: 10 Vties: 76</t>
+  </si>
+  <si>
+    <t>CR: 0.34
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
+    <t>CR: 0.41
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
+    <t>CR: 0.51
+V1: 41 V2: 10 Vties: 89</t>
+  </si>
+  <si>
+    <t>CR: 0.48
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
+    <t>CR: 0.65
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
+    <t>CR: 0.37
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.53
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>CR: 0.78
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>CR: 0.71
+V1: 90 V2: 1 Vties: 50</t>
+  </si>
+  <si>
+    <t>CR: 0.61
+V1: 49 V2: 53 Vties: 16</t>
+  </si>
+  <si>
+    <t>CR: 0.57
+V1: 34 V2: 15 Vties: 92</t>
+  </si>
+  <si>
+    <t>CR: 0.36
+V1: 110 V2: 12 Vties: 20</t>
+  </si>
+  <si>
+    <t>CR: 0.36
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
+    <t>CR: 0.43
+V1: 58 V2: 11 Vties: 72</t>
+  </si>
+  <si>
+    <t>CR: 0.34
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>CR: 0.21
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>CR: 0.25
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>CR: 0.37
 V1: 36 V2: 7 Vties: 99</t>
   </si>
 </sst>
@@ -529,7 +792,7 @@
         <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -546,7 +809,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -568,6 +831,12 @@
       <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
@@ -586,10 +855,376 @@
         <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="112">
   <si>
     <t>Llama-2-7b-chat-hf</t>
   </si>
@@ -46,10 +46,17 @@
     <t>Llama-3.3-70B-Instruct</t>
   </si>
   <si>
+    <t>Qwen3-32B</t>
+  </si>
+  <si>
     <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
     <t>phi-4</t>
+  </si>
+  <si>
+    <t>ASR: 0.74
+V1: 136 V2: 3 Vties: 2</t>
   </si>
   <si>
     <t>ASR: 0.20
@@ -64,6 +71,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>ASR: 0.83
+V1: 95 V2: 34 Vties: 12</t>
+  </si>
+  <si>
     <t>ASR: 0.81
 V1: 81 V2: 19 Vties: 42</t>
   </si>
@@ -80,6 +91,10 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
+    <t>ASR: 0.88
+V1: 98 V2: 30 Vties: 14</t>
+  </si>
+  <si>
     <t>ASR: 0.41
 V1: 92 V2: 16 Vties: 34</t>
   </si>
@@ -124,6 +139,10 @@
 V1: 58 V2: 29 Vties: 55</t>
   </si>
   <si>
+    <t>ASR: 0.94
+V1: 86 V2: 35 Vties: 21</t>
+  </si>
+  <si>
     <t>ASR: 0.95
 V1: 58 V2: 12 Vties: 72</t>
   </si>
@@ -137,6 +156,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 136 V2: 3 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
@@ -149,6 +172,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 95 V2: 34 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 81 V2: 19 Vties: 42</t>
   </si>
   <si>
@@ -165,6 +192,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 98 V2: 30 Vties: 14</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 92 V2: 16 Vties: 34</t>
   </si>
   <si>
@@ -209,6 +240,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 86 V2: 35 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
@@ -218,6 +253,10 @@
   <si>
     <t>AASR: 0.00
 V1: 36 V2: 7 Vties: 99</t>
+  </si>
+  <si>
+    <t>FR: 0.73
+V1: 136 V2: 3 Vties: 2</t>
   </si>
   <si>
     <t>FR: 0.26
@@ -232,6 +271,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>FR: 0.65
+V1: 95 V2: 34 Vties: 12</t>
+  </si>
+  <si>
     <t>FR: 0.76
 V1: 81 V2: 19 Vties: 42</t>
   </si>
@@ -248,6 +291,10 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
+    <t>FR: 0.70
+V1: 98 V2: 30 Vties: 14</t>
+  </si>
+  <si>
     <t>FR: 0.51
 V1: 92 V2: 16 Vties: 34</t>
   </si>
@@ -292,6 +339,10 @@
 V1: 58 V2: 29 Vties: 55</t>
   </si>
   <si>
+    <t>FR: 0.72
+V1: 86 V2: 35 Vties: 21</t>
+  </si>
+  <si>
     <t>FR: 0.89
 V1: 58 V2: 12 Vties: 72</t>
   </si>
@@ -304,6 +355,10 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>CR: 0.27
+V1: 136 V2: 3 Vties: 2</t>
+  </si>
+  <si>
     <t>CR: 0.80
 V1: 129 V2: 2 Vties: 11</t>
   </si>
@@ -316,6 +371,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>CR: 0.39
+V1: 95 V2: 34 Vties: 12</t>
+  </si>
+  <si>
     <t>CR: 0.34
 V1: 81 V2: 19 Vties: 42</t>
   </si>
@@ -332,6 +391,10 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
+    <t>CR: 0.33
+V1: 98 V2: 30 Vties: 14</t>
+  </si>
+  <si>
     <t>CR: 0.65
 V1: 92 V2: 16 Vties: 34</t>
   </si>
@@ -374,6 +437,10 @@
   <si>
     <t>CR: 0.34
 V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>CR: 0.33
+V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
     <t>CR: 0.21
@@ -746,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -783,16 +850,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -800,16 +867,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,48 +884,65 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -905,16 +989,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -922,16 +1006,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -939,48 +1023,65 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>52</v>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -1027,16 +1128,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1044,16 +1145,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1061,48 +1162,65 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>73</v>
+      <c r="E6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -1149,16 +1267,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1166,16 +1284,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1183,48 +1301,65 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>94</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
